--- a/research/traditional_assets/database/data/estonia/estonia_apparel.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_apparel.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.225</v>
+        <v>-0.276</v>
       </c>
       <c r="G2">
-        <v>-0.2509677419354839</v>
+        <v>-0.2359307359307359</v>
       </c>
       <c r="H2">
-        <v>-0.2509677419354839</v>
+        <v>-0.2359307359307359</v>
       </c>
       <c r="I2">
-        <v>-0.6212903225806452</v>
+        <v>-0.3712121212121212</v>
       </c>
       <c r="J2">
-        <v>-0.6212903225806452</v>
+        <v>-0.3641623954680334</v>
       </c>
       <c r="K2">
-        <v>-3.9</v>
+        <v>3.31</v>
       </c>
       <c r="L2">
-        <v>-0.2516129032258064</v>
+        <v>0.3582251082251082</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +624,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.896</v>
+        <v>0.277</v>
       </c>
       <c r="V2">
-        <v>0.05635220125786163</v>
+        <v>0.03239766081871345</v>
       </c>
       <c r="W2">
-        <v>-3.482142857142857</v>
+        <v>4.066339066339067</v>
       </c>
       <c r="X2">
-        <v>0.07829881522445005</v>
+        <v>0.1466103925078073</v>
       </c>
       <c r="Y2">
-        <v>-3.560441672367307</v>
+        <v>3.919728673831259</v>
       </c>
       <c r="Z2">
-        <v>0.8923944959410444</v>
+        <v>0.97571277719113</v>
       </c>
       <c r="AA2">
-        <v>-0.5544360642524038</v>
+        <v>-0.3553179022306895</v>
       </c>
       <c r="AB2">
-        <v>0.05888522243778922</v>
+        <v>0.09594606351237048</v>
       </c>
       <c r="AC2">
-        <v>-0.613321286690193</v>
+        <v>-0.4512639657430599</v>
       </c>
       <c r="AD2">
-        <v>9.73</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>9.73</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AG2">
-        <v>8.834</v>
+        <v>8.183000000000002</v>
       </c>
       <c r="AH2">
-        <v>0.3796332422941865</v>
+        <v>0.4973544973544974</v>
       </c>
       <c r="AI2">
-        <v>0.9227996965098634</v>
+        <v>0.6532818532818533</v>
       </c>
       <c r="AJ2">
-        <v>0.3571601843616075</v>
+        <v>0.4890336460885675</v>
       </c>
       <c r="AK2">
-        <v>0.9156301824212272</v>
+        <v>0.6457034640574449</v>
       </c>
       <c r="AL2">
-        <v>0.437</v>
+        <v>0.297</v>
       </c>
       <c r="AM2">
-        <v>0.437</v>
+        <v>0.297</v>
       </c>
       <c r="AN2">
-        <v>-1.07040704070407</v>
+        <v>-2.782894736842105</v>
       </c>
       <c r="AO2">
-        <v>-22.03661327231121</v>
+        <v>-11.54882154882155</v>
       </c>
       <c r="AP2">
-        <v>-0.9718371837183718</v>
+        <v>-2.691776315789474</v>
       </c>
       <c r="AQ2">
-        <v>-22.03661327231121</v>
+        <v>-11.54882154882155</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.225</v>
+        <v>-0.276</v>
       </c>
       <c r="G3">
-        <v>-0.2509677419354839</v>
+        <v>-0.2359307359307359</v>
       </c>
       <c r="H3">
-        <v>-0.2509677419354839</v>
+        <v>-0.2359307359307359</v>
       </c>
       <c r="I3">
-        <v>-0.6212903225806452</v>
+        <v>-0.3712121212121212</v>
       </c>
       <c r="J3">
-        <v>-0.6212903225806452</v>
+        <v>-0.3641623954680334</v>
       </c>
       <c r="K3">
-        <v>-3.9</v>
+        <v>3.31</v>
       </c>
       <c r="L3">
-        <v>-0.2516129032258064</v>
+        <v>0.3582251082251082</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +743,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +752,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.896</v>
+        <v>0.277</v>
       </c>
       <c r="V3">
-        <v>0.05635220125786163</v>
+        <v>0.03239766081871345</v>
       </c>
       <c r="W3">
-        <v>-3.482142857142857</v>
+        <v>4.066339066339067</v>
       </c>
       <c r="X3">
-        <v>0.07829881522445005</v>
+        <v>0.1466103925078073</v>
       </c>
       <c r="Y3">
-        <v>-3.560441672367307</v>
+        <v>3.919728673831259</v>
       </c>
       <c r="Z3">
-        <v>0.8923944959410444</v>
+        <v>0.97571277719113</v>
       </c>
       <c r="AA3">
-        <v>-0.5544360642524038</v>
+        <v>-0.3553179022306895</v>
       </c>
       <c r="AB3">
-        <v>0.05888522243778922</v>
+        <v>0.09594606351237048</v>
       </c>
       <c r="AC3">
-        <v>-0.613321286690193</v>
+        <v>-0.4512639657430599</v>
       </c>
       <c r="AD3">
-        <v>9.73</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>9.73</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AG3">
-        <v>8.834</v>
+        <v>8.183000000000002</v>
       </c>
       <c r="AH3">
-        <v>0.3796332422941865</v>
+        <v>0.4973544973544974</v>
       </c>
       <c r="AI3">
-        <v>0.9227996965098634</v>
+        <v>0.6532818532818533</v>
       </c>
       <c r="AJ3">
-        <v>0.3571601843616075</v>
+        <v>0.4890336460885675</v>
       </c>
       <c r="AK3">
-        <v>0.9156301824212272</v>
+        <v>0.6457034640574449</v>
       </c>
       <c r="AL3">
-        <v>0.437</v>
+        <v>0.297</v>
       </c>
       <c r="AM3">
-        <v>0.437</v>
+        <v>0.297</v>
       </c>
       <c r="AN3">
-        <v>-1.07040704070407</v>
+        <v>-2.782894736842105</v>
       </c>
       <c r="AO3">
-        <v>-22.03661327231121</v>
+        <v>-11.54882154882155</v>
       </c>
       <c r="AP3">
-        <v>-0.9718371837183718</v>
+        <v>-2.691776315789474</v>
       </c>
       <c r="AQ3">
-        <v>-22.03661327231121</v>
+        <v>-11.54882154882155</v>
       </c>
     </row>
   </sheetData>
